--- a/public/plantillas/plantilla-importacion-cargios.xlsx
+++ b/public/plantillas/plantilla-importacion-cargios.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wonka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9576E3D-239A-4EF0-9084-3381DFD59AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C97818B-94D2-41CB-AC43-20B6CEB58906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12225" yWindow="3870" windowWidth="20310" windowHeight="16395" xr2:uid="{95A3EB81-5420-4EF6-92DC-587B5E595DDC}"/>
+    <workbookView xWindow="28020" yWindow="4005" windowWidth="20310" windowHeight="16395" activeTab="2" xr2:uid="{95A3EB81-5420-4EF6-92DC-587B5E595DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="13">
   <si>
     <t>EESS</t>
   </si>
@@ -82,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +97,21 @@
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Anh_font_ttf"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Anh_font_ttf"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -138,12 +155,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,4 +787,616 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7425CD8-20A3-4295-A9E9-BDD2B8DE07F8}">
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9BB6-2294-4C00-B7E3-33FCA3801BA1}">
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>